--- a/PRP申請書類 自動転記ツール/99_data/テンプレート/3種筋腱靭帯系PRP/01.【様式第一の二】 再生医療等提供計画 (治療) 整形外科(・三種）.xlsx
+++ b/PRP申請書類 自動転記ツール/99_data/テンプレート/3種筋腱靭帯系PRP/01.【様式第一の二】 再生医療等提供計画 (治療) 整形外科(・三種）.xlsx
@@ -5449,7 +5449,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>{{再生医療①（右記タブから選択）}}</t>
+    <t>{{再生医療②（右記タブから選択）}}</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
